--- a/data_lake/reporte_cordoba_mes/dt=2026-07-26/CORDOBA_JUL26.xlsx
+++ b/data_lake/reporte_cordoba_mes/dt=2026-07-26/CORDOBA_JUL26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.187.8\Oficina\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883651A1-2CDB-42EF-8815-1E4E19435BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936374C-149C-425E-916F-75E07171A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F8F14AC-D557-4126-B18A-7A2C1E69122F}"/>
   </bookViews>
@@ -10032,7 +10032,7 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1</c:v>
+                  <c:v>109.8</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-1</c:v>
@@ -19988,8 +19988,12 @@
       <c r="AA3" s="25">
         <v>64.5</v>
       </c>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
+      <c r="AB3" s="25">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="25">
+        <v>7.3</v>
+      </c>
       <c r="AD3" s="25"/>
       <c r="AE3" s="25"/>
       <c r="AF3" s="25"/>
@@ -19998,7 +20002,7 @@
       <c r="AI3" s="34"/>
       <c r="AJ3" s="36">
         <f>SUM(E3:AI3)</f>
-        <v>191.3</v>
+        <v>198.60000000000002</v>
       </c>
       <c r="AK3" s="30">
         <v>27.817857142857147</v>
@@ -20089,7 +20093,9 @@
       <c r="AB4" s="25">
         <v>0</v>
       </c>
-      <c r="AC4" s="25"/>
+      <c r="AC4" s="25">
+        <v>0</v>
+      </c>
       <c r="AD4" s="25"/>
       <c r="AE4" s="25"/>
       <c r="AF4" s="25"/>
@@ -20189,7 +20195,9 @@
       <c r="AB5" s="25">
         <v>0</v>
       </c>
-      <c r="AC5" s="25"/>
+      <c r="AC5" s="25">
+        <v>41.4</v>
+      </c>
       <c r="AD5" s="25"/>
       <c r="AE5" s="25"/>
       <c r="AF5" s="25"/>
@@ -20198,7 +20206,7 @@
       <c r="AI5" s="34"/>
       <c r="AJ5" s="36">
         <f t="shared" si="0"/>
-        <v>207</v>
+        <v>248.4</v>
       </c>
       <c r="AK5" s="30">
         <v>40.986206896551728</v>
@@ -20289,7 +20297,9 @@
       <c r="AB6" s="25">
         <v>0.5</v>
       </c>
-      <c r="AC6" s="25"/>
+      <c r="AC6" s="25">
+        <v>15.5</v>
+      </c>
       <c r="AD6" s="25"/>
       <c r="AE6" s="25"/>
       <c r="AF6" s="25"/>
@@ -20298,7 +20308,7 @@
       <c r="AI6" s="34"/>
       <c r="AJ6" s="36">
         <f t="shared" si="0"/>
-        <v>125.80000000000001</v>
+        <v>141.30000000000001</v>
       </c>
       <c r="AK6" s="30">
         <v>88.719230769230762</v>
@@ -20493,7 +20503,9 @@
       <c r="AB9" s="25">
         <v>0</v>
       </c>
-      <c r="AC9" s="25"/>
+      <c r="AC9" s="25">
+        <v>6</v>
+      </c>
       <c r="AD9" s="25"/>
       <c r="AE9" s="25"/>
       <c r="AF9" s="25"/>
@@ -20502,7 +20514,7 @@
       <c r="AI9" s="34"/>
       <c r="AJ9" s="36">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AK9" s="30">
         <v>65.482758620689651</v>
@@ -20669,7 +20681,9 @@
       <c r="AB11" s="25">
         <v>0</v>
       </c>
-      <c r="AC11" s="25"/>
+      <c r="AC11" s="25">
+        <v>4.2</v>
+      </c>
       <c r="AD11" s="25"/>
       <c r="AE11" s="25"/>
       <c r="AF11" s="25"/>
@@ -20678,7 +20692,7 @@
       <c r="AI11" s="34"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>153.4</v>
+        <v>157.6</v>
       </c>
       <c r="AK11" s="30">
         <v>19.188461538461539</v>
@@ -20767,7 +20781,9 @@
       <c r="AB12" s="25">
         <v>0</v>
       </c>
-      <c r="AC12" s="25"/>
+      <c r="AC12" s="25">
+        <v>0</v>
+      </c>
       <c r="AD12" s="25"/>
       <c r="AE12" s="25"/>
       <c r="AF12" s="25"/>
@@ -20867,7 +20883,9 @@
       <c r="AB13" s="25">
         <v>0</v>
       </c>
-      <c r="AC13" s="25"/>
+      <c r="AC13" s="25">
+        <v>29</v>
+      </c>
       <c r="AD13" s="25"/>
       <c r="AE13" s="25"/>
       <c r="AF13" s="25"/>
@@ -20876,7 +20894,7 @@
       <c r="AI13" s="34"/>
       <c r="AJ13" s="36">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AK13" s="30"/>
     </row>
@@ -20965,7 +20983,9 @@
       <c r="AB14" s="25">
         <v>0</v>
       </c>
-      <c r="AC14" s="25"/>
+      <c r="AC14" s="25">
+        <v>0</v>
+      </c>
       <c r="AD14" s="25"/>
       <c r="AE14" s="25"/>
       <c r="AF14" s="25"/>
@@ -21065,7 +21085,9 @@
       <c r="AB15" s="25">
         <v>0</v>
       </c>
-      <c r="AC15" s="25"/>
+      <c r="AC15" s="25">
+        <v>6.4</v>
+      </c>
       <c r="AD15" s="25"/>
       <c r="AE15" s="25"/>
       <c r="AF15" s="25"/>
@@ -21074,7 +21096,7 @@
       <c r="AI15" s="34"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>136.4</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="AK15" s="30">
         <v>60.46</v>
@@ -21280,7 +21302,7 @@
       </c>
       <c r="AC19" s="26">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>109.8</v>
       </c>
       <c r="AD19" s="26">
         <f t="shared" si="1"/>
